--- a/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/WYOMING_2018.xlsx
+++ b/1_network_estimation/1_data_cleaning/Data_clean/MCAS/Estados_US/Edos_USA_2018/WYOMING_2018.xlsx
@@ -351,28 +351,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D317"/>
+  <dimension ref="A1:D311"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Estado de Origen</t>
+          <t>mx_state</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Municipio Origen</t>
+          <t>mx_municipality</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Número de Matrículas</t>
+          <t>n_matriculas</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Porcentaje de Matrículas</t>
+          <t>pct_matriculas</t>
         </is>
       </c>
     </row>
@@ -395,6 +395,11 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>Calvillo</t>
@@ -408,9 +413,14 @@
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Pabellón de Arteaga</t>
+          <t>Pabellón De Arteaga</t>
         </is>
       </c>
       <c r="C4">
@@ -421,6 +431,11 @@
       </c>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Aguascalientes</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>Total</t>
@@ -452,6 +467,11 @@
       </c>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Baja California</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>Total</t>
@@ -483,6 +503,11 @@
       </c>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>Champotón</t>
@@ -496,6 +521,11 @@
       </c>
     </row>
     <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>Escárcega</t>
@@ -509,6 +539,11 @@
       </c>
     </row>
     <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Campeche</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>Total</t>
@@ -540,9 +575,14 @@
       </c>
     </row>
     <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Amatenango de la Frontera</t>
+          <t>Amatenango De La Frontera</t>
         </is>
       </c>
       <c r="C13">
@@ -553,6 +593,11 @@
       </c>
     </row>
     <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>Cintalapa</t>
@@ -566,6 +611,11 @@
       </c>
     </row>
     <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>Motozintla</t>
@@ -579,6 +629,11 @@
       </c>
     </row>
     <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Chiapas</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>Total</t>
@@ -610,6 +665,11 @@
       </c>
     </row>
     <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>Allende</t>
@@ -623,6 +683,11 @@
       </c>
     </row>
     <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>Ascensión</t>
@@ -636,6 +701,11 @@
       </c>
     </row>
     <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>Bachíniva</t>
@@ -649,6 +719,11 @@
       </c>
     </row>
     <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>Buenaventura</t>
@@ -662,6 +737,11 @@
       </c>
     </row>
     <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>Camargo</t>
@@ -675,6 +755,11 @@
       </c>
     </row>
     <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>Chihuahua</t>
@@ -688,6 +773,11 @@
       </c>
     </row>
     <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -701,6 +791,11 @@
       </c>
     </row>
     <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>Delicias</t>
@@ -714,6 +809,11 @@
       </c>
     </row>
     <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>Dr. Belisario Domínguez</t>
@@ -727,6 +827,11 @@
       </c>
     </row>
     <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>Gómez Farías</t>
@@ -740,6 +845,11 @@
       </c>
     </row>
     <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>Gran Morelos</t>
@@ -753,9 +863,14 @@
       </c>
     </row>
     <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Guadalupe y Calvo</t>
+          <t>Guadalupe Y Calvo</t>
         </is>
       </c>
       <c r="C29">
@@ -766,6 +881,11 @@
       </c>
     </row>
     <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>Guerrero</t>
@@ -779,9 +899,14 @@
       </c>
     </row>
     <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hidalgo del Parral</t>
+          <t>Hidalgo Del Parral</t>
         </is>
       </c>
       <c r="C31">
@@ -792,6 +917,11 @@
       </c>
     </row>
     <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>Ignacio Zaragoza</t>
@@ -805,6 +935,11 @@
       </c>
     </row>
     <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>Juárez</t>
@@ -818,6 +953,11 @@
       </c>
     </row>
     <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>Madera</t>
@@ -831,6 +971,11 @@
       </c>
     </row>
     <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B35" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -844,6 +989,11 @@
       </c>
     </row>
     <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>Meoqui</t>
@@ -857,6 +1007,11 @@
       </c>
     </row>
     <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>Namiquipa</t>
@@ -870,6 +1025,11 @@
       </c>
     </row>
     <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>Nonoava</t>
@@ -883,6 +1043,11 @@
       </c>
     </row>
     <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>Nuevo Casas Grandes</t>
@@ -896,6 +1061,11 @@
       </c>
     </row>
     <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>Rosario</t>
@@ -909,6 +1079,11 @@
       </c>
     </row>
     <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>Santa Bárbara</t>
@@ -922,6 +1097,11 @@
       </c>
     </row>
     <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>Satevó</t>
@@ -935,6 +1115,11 @@
       </c>
     </row>
     <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>Temósachic</t>
@@ -948,6 +1133,11 @@
       </c>
     </row>
     <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Chihuahua</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>Total</t>
@@ -979,6 +1169,11 @@
       </c>
     </row>
     <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B46" t="inlineStr">
         <is>
           <t>Matamoros</t>
@@ -992,6 +1187,11 @@
       </c>
     </row>
     <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>Piedras Negras</t>
@@ -1005,6 +1205,11 @@
       </c>
     </row>
     <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>Torreón</t>
@@ -1018,6 +1223,11 @@
       </c>
     </row>
     <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>Viesca</t>
@@ -1031,6 +1241,11 @@
       </c>
     </row>
     <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Coahuila</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1062,6 +1277,11 @@
       </c>
     </row>
     <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>Tecomán</t>
@@ -1075,6 +1295,11 @@
       </c>
     </row>
     <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Colima</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1090,7 +1315,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Ciudad de México</t>
+          <t>Ciudad De México</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -1106,6 +1331,11 @@
       </c>
     </row>
     <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>Azcapotzalco</t>
@@ -1119,6 +1349,11 @@
       </c>
     </row>
     <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1132,6 +1367,11 @@
       </c>
     </row>
     <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B57" t="inlineStr">
         <is>
           <t>Coyoacán</t>
@@ -1145,6 +1385,11 @@
       </c>
     </row>
     <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>Cuauhtémoc</t>
@@ -1158,6 +1403,11 @@
       </c>
     </row>
     <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>Gustavo A. Madero</t>
@@ -1171,6 +1421,11 @@
       </c>
     </row>
     <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>Iztacalco</t>
@@ -1184,6 +1439,11 @@
       </c>
     </row>
     <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>Iztapalapa</t>
@@ -1197,6 +1457,11 @@
       </c>
     </row>
     <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>La Magdalena Contreras</t>
@@ -1210,6 +1475,11 @@
       </c>
     </row>
     <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>Miguel Hidalgo</t>
@@ -1223,6 +1493,11 @@
       </c>
     </row>
     <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>Tlalpan</t>
@@ -1236,6 +1511,11 @@
       </c>
     </row>
     <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>Venustiano Carranza</t>
@@ -1249,6 +1529,11 @@
       </c>
     </row>
     <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>Xochimilco</t>
@@ -1262,6 +1547,11 @@
       </c>
     </row>
     <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ciudad De México</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1282,7 +1572,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Coneto de Comonfort</t>
+          <t>Coneto De Comonfort</t>
         </is>
       </c>
       <c r="C68">
@@ -1293,6 +1583,11 @@
       </c>
     </row>
     <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>Cuencamé</t>
@@ -1306,6 +1601,11 @@
       </c>
     </row>
     <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>Durango</t>
@@ -1319,6 +1619,11 @@
       </c>
     </row>
     <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>Gómez Palacio</t>
@@ -1332,6 +1637,11 @@
       </c>
     </row>
     <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>Guadalupe Victoria</t>
@@ -1345,6 +1655,11 @@
       </c>
     </row>
     <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>Lerdo</t>
@@ -1358,6 +1673,11 @@
       </c>
     </row>
     <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>Mapimí</t>
@@ -1371,9 +1691,14 @@
       </c>
     </row>
     <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Nombre de Dios</t>
+          <t>Nombre De Dios</t>
         </is>
       </c>
       <c r="C75">
@@ -1384,6 +1709,11 @@
       </c>
     </row>
     <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>Ocampo</t>
@@ -1397,6 +1727,11 @@
       </c>
     </row>
     <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>Otáez</t>
@@ -1410,6 +1745,11 @@
       </c>
     </row>
     <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>San Bernardo</t>
@@ -1423,6 +1763,11 @@
       </c>
     </row>
     <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B79" t="inlineStr">
         <is>
           <t>San Dimas</t>
@@ -1436,9 +1781,14 @@
       </c>
     </row>
     <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>San Juan del Río</t>
+          <t>San Juan Del Río</t>
         </is>
       </c>
       <c r="C80">
@@ -1449,6 +1799,11 @@
       </c>
     </row>
     <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>Súchil</t>
@@ -1462,6 +1817,11 @@
       </c>
     </row>
     <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>Vicente Guerrero</t>
@@ -1475,6 +1835,11 @@
       </c>
     </row>
     <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Durango</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1490,12 +1855,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Estado de México</t>
+          <t>Estado De México</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Acambay de Ruíz Castañeda</t>
+          <t>Acambay De Ruíz Castañeda</t>
         </is>
       </c>
       <c r="C84">
@@ -1506,6 +1871,11 @@
       </c>
     </row>
     <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>Aculco</t>
@@ -1519,6 +1889,11 @@
       </c>
     </row>
     <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>Atlautla</t>
@@ -1532,6 +1907,11 @@
       </c>
     </row>
     <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>Chimalhuacán</t>
@@ -1545,9 +1925,14 @@
       </c>
     </row>
     <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Ecatepec de Morelos</t>
+          <t>Ecatepec De Morelos</t>
         </is>
       </c>
       <c r="C88">
@@ -1558,6 +1943,11 @@
       </c>
     </row>
     <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>Ixtlahuaca</t>
@@ -1571,6 +1961,11 @@
       </c>
     </row>
     <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B90" t="inlineStr">
         <is>
           <t>La Paz</t>
@@ -1584,6 +1979,11 @@
       </c>
     </row>
     <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>Metepec</t>
@@ -1597,6 +1997,11 @@
       </c>
     </row>
     <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>Nezahualcóyotl</t>
@@ -1610,6 +2015,11 @@
       </c>
     </row>
     <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>Temascaltepec</t>
@@ -1623,6 +2033,11 @@
       </c>
     </row>
     <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>Texcoco</t>
@@ -1636,9 +2051,14 @@
       </c>
     </row>
     <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Tlalnepantla de Baz</t>
+          <t>Tlalnepantla De Baz</t>
         </is>
       </c>
       <c r="C95">
@@ -1649,6 +2069,11 @@
       </c>
     </row>
     <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>Toluca</t>
@@ -1662,6 +2087,11 @@
       </c>
     </row>
     <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>Villa Victoria</t>
@@ -1675,6 +2105,11 @@
       </c>
     </row>
     <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Estado De México</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1706,6 +2141,11 @@
       </c>
     </row>
     <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>Celaya</t>
@@ -1719,6 +2159,11 @@
       </c>
     </row>
     <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B101" t="inlineStr">
         <is>
           <t>Cortazar</t>
@@ -1732,6 +2177,11 @@
       </c>
     </row>
     <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>Cuerámaro</t>
@@ -1745,9 +2195,14 @@
       </c>
     </row>
     <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna de la Independencia Nacional</t>
+          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
         </is>
       </c>
       <c r="C103">
@@ -1758,6 +2213,11 @@
       </c>
     </row>
     <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>Irapuato</t>
@@ -1771,6 +2231,11 @@
       </c>
     </row>
     <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>Jerécuaro</t>
@@ -1784,6 +2249,11 @@
       </c>
     </row>
     <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>León</t>
@@ -1797,6 +2267,11 @@
       </c>
     </row>
     <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>Pénjamo</t>
@@ -1810,6 +2285,11 @@
       </c>
     </row>
     <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>Romita</t>
@@ -1823,9 +2303,14 @@
       </c>
     </row>
     <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>San Francisco del Rincón</t>
+          <t>San Francisco Del Rincón</t>
         </is>
       </c>
       <c r="C109">
@@ -1836,6 +2321,11 @@
       </c>
     </row>
     <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>San José Iturbide</t>
@@ -1849,9 +2339,14 @@
       </c>
     </row>
     <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>San Luis de la Paz</t>
+          <t>San Luis De La Paz</t>
         </is>
       </c>
       <c r="C111">
@@ -1862,9 +2357,14 @@
       </c>
     </row>
     <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Silao de la Victoria</t>
+          <t>Silao De La Victoria</t>
         </is>
       </c>
       <c r="C112">
@@ -1875,9 +2375,14 @@
       </c>
     </row>
     <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Valle de Santiago</t>
+          <t>Valle De Santiago</t>
         </is>
       </c>
       <c r="C113">
@@ -1888,6 +2393,11 @@
       </c>
     </row>
     <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>Yuriria</t>
@@ -1901,6 +2411,11 @@
       </c>
     </row>
     <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Guanajuato</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>Total</t>
@@ -1921,7 +2436,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Acapulco de Juárez</t>
+          <t>Acapulco De Juárez</t>
         </is>
       </c>
       <c r="C116">
@@ -1932,6 +2447,11 @@
       </c>
     </row>
     <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>Arcelia</t>
@@ -1945,6 +2465,11 @@
       </c>
     </row>
     <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>Benito Juárez</t>
@@ -1958,6 +2483,11 @@
       </c>
     </row>
     <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>Copalillo</t>
@@ -1971,9 +2501,14 @@
       </c>
     </row>
     <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Coyuca de Benítez</t>
+          <t>Coyuca De Benítez</t>
         </is>
       </c>
       <c r="C120">
@@ -1984,6 +2519,11 @@
       </c>
     </row>
     <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>Juan R. Escudero</t>
@@ -1997,6 +2537,11 @@
       </c>
     </row>
     <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>Leonardo Bravo</t>
@@ -2010,6 +2555,11 @@
       </c>
     </row>
     <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B123" t="inlineStr">
         <is>
           <t>Tecoanapa</t>
@@ -2023,9 +2573,14 @@
       </c>
     </row>
     <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Técpan de Galeana</t>
+          <t>Técpan De Galeana</t>
         </is>
       </c>
       <c r="C124">
@@ -2036,6 +2591,11 @@
       </c>
     </row>
     <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Guerrero</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2067,9 +2627,14 @@
       </c>
     </row>
     <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Atotonilco el Grande</t>
+          <t>Atotonilco El Grande</t>
         </is>
       </c>
       <c r="C127">
@@ -2080,6 +2645,11 @@
       </c>
     </row>
     <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>Huichapan</t>
@@ -2093,6 +2663,11 @@
       </c>
     </row>
     <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>Tecozautla</t>
@@ -2106,6 +2681,11 @@
       </c>
     </row>
     <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>Tlahuiltepa</t>
@@ -2119,6 +2699,11 @@
       </c>
     </row>
     <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>Zimapán</t>
@@ -2132,6 +2717,11 @@
       </c>
     </row>
     <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Hidalgo</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2163,9 +2753,14 @@
       </c>
     </row>
     <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Autlán de Navarro</t>
+          <t>Autlán De Navarro</t>
         </is>
       </c>
       <c r="C134">
@@ -2176,6 +2771,11 @@
       </c>
     </row>
     <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>Ayutla</t>
@@ -2189,6 +2789,11 @@
       </c>
     </row>
     <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>Colotlán</t>
@@ -2202,6 +2807,11 @@
       </c>
     </row>
     <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>Cuquío</t>
@@ -2215,6 +2825,11 @@
       </c>
     </row>
     <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>Ejutla</t>
@@ -2228,6 +2843,11 @@
       </c>
     </row>
     <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>Guadalajara</t>
@@ -2241,9 +2861,14 @@
       </c>
     </row>
     <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Huejuquilla el Alto</t>
+          <t>Huejuquilla El Alto</t>
         </is>
       </c>
       <c r="C140">
@@ -2254,9 +2879,14 @@
       </c>
     </row>
     <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Lagos de Moreno</t>
+          <t>Lagos De Moreno</t>
         </is>
       </c>
       <c r="C141">
@@ -2267,6 +2897,11 @@
       </c>
     </row>
     <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>Magdalena</t>
@@ -2280,6 +2915,11 @@
       </c>
     </row>
     <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>Pihuamo</t>
@@ -2293,6 +2933,11 @@
       </c>
     </row>
     <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>Puerto Vallarta</t>
@@ -2306,6 +2951,11 @@
       </c>
     </row>
     <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B145" t="inlineStr">
         <is>
           <t>Quitupan</t>
@@ -2319,9 +2969,14 @@
       </c>
     </row>
     <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>San Diego de Alejandría</t>
+          <t>San Diego De Alejandría</t>
         </is>
       </c>
       <c r="C146">
@@ -2332,9 +2987,14 @@
       </c>
     </row>
     <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>San Juan de los Lagos</t>
+          <t>San Juan De Los Lagos</t>
         </is>
       </c>
       <c r="C147">
@@ -2345,6 +3005,11 @@
       </c>
     </row>
     <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>San Julián</t>
@@ -2358,9 +3023,14 @@
       </c>
     </row>
     <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>San Miguel el Alto</t>
+          <t>San Miguel El Alto</t>
         </is>
       </c>
       <c r="C149">
@@ -2371,6 +3041,11 @@
       </c>
     </row>
     <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>Tala</t>
@@ -2384,9 +3059,14 @@
       </c>
     </row>
     <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Tamazula de Gordiano</t>
+          <t>Tamazula De Gordiano</t>
         </is>
       </c>
       <c r="C151">
@@ -2397,9 +3077,14 @@
       </c>
     </row>
     <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Tepatitlán de Morelos</t>
+          <t>Tepatitlán De Morelos</t>
         </is>
       </c>
       <c r="C152">
@@ -2410,9 +3095,14 @@
       </c>
     </row>
     <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Tlajomulco de Zúñiga</t>
+          <t>Tlajomulco De Zúñiga</t>
         </is>
       </c>
       <c r="C153">
@@ -2423,6 +3113,11 @@
       </c>
     </row>
     <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>San Pedro Tlaquepaque</t>
@@ -2436,6 +3131,11 @@
       </c>
     </row>
     <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>Tomatlán</t>
@@ -2449,9 +3149,14 @@
       </c>
     </row>
     <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Unión de Tula</t>
+          <t>Unión De Tula</t>
         </is>
       </c>
       <c r="C156">
@@ -2462,6 +3167,11 @@
       </c>
     </row>
     <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>Villa Purificación</t>
@@ -2475,9 +3185,14 @@
       </c>
     </row>
     <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Zacoalco de Torres</t>
+          <t>Zacoalco De Torres</t>
         </is>
       </c>
       <c r="C158">
@@ -2488,9 +3203,14 @@
       </c>
     </row>
     <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Zapotlán el Grande</t>
+          <t>Zapotlán El Grande</t>
         </is>
       </c>
       <c r="C159">
@@ -2501,6 +3221,11 @@
       </c>
     </row>
     <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Jalisco</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2532,6 +3257,11 @@
       </c>
     </row>
     <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>Ario</t>
@@ -2545,6 +3275,11 @@
       </c>
     </row>
     <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>Buenavista</t>
@@ -2558,6 +3293,11 @@
       </c>
     </row>
     <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>Charo</t>
@@ -2571,6 +3311,11 @@
       </c>
     </row>
     <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>Chavinda</t>
@@ -2584,6 +3329,11 @@
       </c>
     </row>
     <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>Contepec</t>
@@ -2597,6 +3347,11 @@
       </c>
     </row>
     <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>Copándaro</t>
@@ -2610,6 +3365,11 @@
       </c>
     </row>
     <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>Jiménez</t>
@@ -2623,6 +3383,11 @@
       </c>
     </row>
     <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>La Piedad</t>
@@ -2636,6 +3401,11 @@
       </c>
     </row>
     <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>Morelia</t>
@@ -2649,6 +3419,11 @@
       </c>
     </row>
     <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>Queréndaro</t>
@@ -2662,6 +3437,11 @@
       </c>
     </row>
     <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B172" t="inlineStr">
         <is>
           <t>Sahuayo</t>
@@ -2675,6 +3455,11 @@
       </c>
     </row>
     <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>Santa Ana Maya</t>
@@ -2688,6 +3473,11 @@
       </c>
     </row>
     <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>Tacámbaro</t>
@@ -2701,6 +3491,11 @@
       </c>
     </row>
     <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>Tepalcatepec</t>
@@ -2714,6 +3509,11 @@
       </c>
     </row>
     <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>Tuxpan</t>
@@ -2727,6 +3527,11 @@
       </c>
     </row>
     <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>Yurécuaro</t>
@@ -2740,6 +3545,11 @@
       </c>
     </row>
     <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>Zacapu</t>
@@ -2753,6 +3563,11 @@
       </c>
     </row>
     <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>Zamora</t>
@@ -2766,6 +3581,11 @@
       </c>
     </row>
     <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>Zinapécuaro</t>
@@ -2779,6 +3599,11 @@
       </c>
     </row>
     <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>Zitácuaro</t>
@@ -2792,6 +3617,11 @@
       </c>
     </row>
     <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Michoacán</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2823,6 +3653,11 @@
       </c>
     </row>
     <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>Cuernavaca</t>
@@ -2836,6 +3671,11 @@
       </c>
     </row>
     <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Morelos</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2867,9 +3707,14 @@
       </c>
     </row>
     <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Santa María del Oro</t>
+          <t>Santa María Del Oro</t>
         </is>
       </c>
       <c r="C187">
@@ -2880,6 +3725,11 @@
       </c>
     </row>
     <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>Tecuala</t>
@@ -2893,6 +3743,11 @@
       </c>
     </row>
     <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>Tepic</t>
@@ -2906,6 +3761,11 @@
       </c>
     </row>
     <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Nayarit</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2937,6 +3797,11 @@
       </c>
     </row>
     <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Nuevo León</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>Total</t>
@@ -2968,9 +3833,14 @@
       </c>
     </row>
     <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Heroica Ciudad de Juchitán de Zaragoza</t>
+          <t>Heroica Ciudad De Juchitán De Zaragoza</t>
         </is>
       </c>
       <c r="C194">
@@ -2981,6 +3851,11 @@
       </c>
     </row>
     <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>Matías Romero Avendaño</t>
@@ -2994,9 +3869,14 @@
       </c>
     </row>
     <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Oaxaca de Juárez</t>
+          <t>Oaxaca De Juárez</t>
         </is>
       </c>
       <c r="C196">
@@ -3007,9 +3887,14 @@
       </c>
     </row>
     <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Ocotlán de Morelos</t>
+          <t>Ocotlán De Morelos</t>
         </is>
       </c>
       <c r="C197">
@@ -3020,6 +3905,11 @@
       </c>
     </row>
     <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>San Andrés Solaga</t>
@@ -3033,6 +3923,11 @@
       </c>
     </row>
     <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>San Francisco Teopan</t>
@@ -3046,6 +3941,11 @@
       </c>
     </row>
     <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>San Juan Bautista Tuxtepec</t>
@@ -3059,6 +3959,11 @@
       </c>
     </row>
     <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>San Mateo Cajonos</t>
@@ -3072,6 +3977,11 @@
       </c>
     </row>
     <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>San Pedro Mártir</t>
@@ -3085,6 +3995,11 @@
       </c>
     </row>
     <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>Santa Catarina Juquila</t>
@@ -3098,6 +4013,11 @@
       </c>
     </row>
     <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>Santiago Jocotepec</t>
@@ -3111,6 +4031,11 @@
       </c>
     </row>
     <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B205" t="inlineStr">
         <is>
           <t>Santiago Pinotepa Nacional</t>
@@ -3124,6 +4049,11 @@
       </c>
     </row>
     <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>Santiago Yosondúa</t>
@@ -3137,6 +4067,11 @@
       </c>
     </row>
     <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>Silacayoápam</t>
@@ -3150,9 +4085,14 @@
       </c>
     </row>
     <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Tlacolula de Matamoros</t>
+          <t>Tlacolula De Matamoros</t>
         </is>
       </c>
       <c r="C208">
@@ -3163,6 +4103,11 @@
       </c>
     </row>
     <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Oaxaca</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3194,9 +4139,14 @@
       </c>
     </row>
     <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Chalchicomula de Sesma</t>
+          <t>Chalchicomula De Sesma</t>
         </is>
       </c>
       <c r="C211">
@@ -3207,6 +4157,11 @@
       </c>
     </row>
     <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>Chignahuapan</t>
@@ -3220,6 +4175,11 @@
       </c>
     </row>
     <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>Ixtacamaxtitlán</t>
@@ -3233,6 +4193,11 @@
       </c>
     </row>
     <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>Jopala</t>
@@ -3246,6 +4211,11 @@
       </c>
     </row>
     <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>Piaxtla</t>
@@ -3259,6 +4229,11 @@
       </c>
     </row>
     <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B216" t="inlineStr">
         <is>
           <t>Puebla</t>
@@ -3272,6 +4247,11 @@
       </c>
     </row>
     <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>San Pedro Cholula</t>
@@ -3285,6 +4265,11 @@
       </c>
     </row>
     <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>Teotlalco</t>
@@ -3298,6 +4283,11 @@
       </c>
     </row>
     <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>Tepeaca</t>
@@ -3311,6 +4301,11 @@
       </c>
     </row>
     <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>Teziutlán</t>
@@ -3324,9 +4319,14 @@
       </c>
     </row>
     <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Tlacotepec de Benito Juárez</t>
+          <t>Tlacotepec De Benito Juárez</t>
         </is>
       </c>
       <c r="C221">
@@ -3337,6 +4337,11 @@
       </c>
     </row>
     <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>Tlaola</t>
@@ -3350,6 +4355,11 @@
       </c>
     </row>
     <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>Tlapacoya</t>
@@ -3363,6 +4373,11 @@
       </c>
     </row>
     <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>Yehualtepec</t>
@@ -3376,6 +4391,11 @@
       </c>
     </row>
     <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>Zacatlán</t>
@@ -3389,6 +4409,11 @@
       </c>
     </row>
     <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>Zihuateutla</t>
@@ -3402,6 +4427,11 @@
       </c>
     </row>
     <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>Puebla</t>
+        </is>
+      </c>
       <c r="B227" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3422,7 +4452,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Cadereyta de Montes</t>
+          <t>Cadereyta De Montes</t>
         </is>
       </c>
       <c r="C228">
@@ -3433,6 +4463,11 @@
       </c>
     </row>
     <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>Peñamiller</t>
@@ -3446,6 +4481,11 @@
       </c>
     </row>
     <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>Querétaro</t>
@@ -3459,6 +4499,11 @@
       </c>
     </row>
     <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>Querétaro</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3490,9 +4535,14 @@
       </c>
     </row>
     <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>San Ciro de Acosta</t>
+          <t>San Ciro De Acosta</t>
         </is>
       </c>
       <c r="C233">
@@ -3503,6 +4553,11 @@
       </c>
     </row>
     <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>San Luis Potosí</t>
@@ -3516,9 +4571,14 @@
       </c>
     </row>
     <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Santa María del Río</t>
+          <t>Santa María Del Río</t>
         </is>
       </c>
       <c r="C235">
@@ -3529,9 +4589,14 @@
       </c>
     </row>
     <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Villa de Ramos</t>
+          <t>Villa De Ramos</t>
         </is>
       </c>
       <c r="C236">
@@ -3542,6 +4607,11 @@
       </c>
     </row>
     <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>San Luis Potosí</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3573,6 +4643,11 @@
       </c>
     </row>
     <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>Angostura</t>
@@ -3586,6 +4661,11 @@
       </c>
     </row>
     <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>Culiacán</t>
@@ -3599,6 +4679,11 @@
       </c>
     </row>
     <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>Escuinapa</t>
@@ -3612,6 +4697,11 @@
       </c>
     </row>
     <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>Guasave</t>
@@ -3625,6 +4715,11 @@
       </c>
     </row>
     <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>Mocorito</t>
@@ -3638,6 +4733,11 @@
       </c>
     </row>
     <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>Sinaloa</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3669,6 +4769,11 @@
       </c>
     </row>
     <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>Bácum</t>
@@ -3682,6 +4787,11 @@
       </c>
     </row>
     <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>Caborca</t>
@@ -3695,6 +4805,11 @@
       </c>
     </row>
     <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>Cajeme</t>
@@ -3708,6 +4823,11 @@
       </c>
     </row>
     <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B249" t="inlineStr">
         <is>
           <t>Empalme</t>
@@ -3721,6 +4841,11 @@
       </c>
     </row>
     <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>Guaymas</t>
@@ -3734,6 +4859,11 @@
       </c>
     </row>
     <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>Hermosillo</t>
@@ -3747,6 +4877,11 @@
       </c>
     </row>
     <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>Sahuaripa</t>
@@ -3760,6 +4895,11 @@
       </c>
     </row>
     <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>San Luis Río Colorado</t>
@@ -3773,6 +4913,11 @@
       </c>
     </row>
     <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>Sonora</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3804,6 +4949,11 @@
       </c>
     </row>
     <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>Macuspana</t>
@@ -3817,6 +4967,11 @@
       </c>
     </row>
     <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>Tabasco</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3848,6 +5003,11 @@
       </c>
     </row>
     <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>Tamaulipas</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>Total</t>
@@ -3879,6 +5039,11 @@
       </c>
     </row>
     <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>Atlangatepec</t>
@@ -3892,6 +5057,11 @@
       </c>
     </row>
     <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>Chiautempan</t>
@@ -3905,6 +5075,11 @@
       </c>
     </row>
     <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>Cuaxomulco</t>
@@ -3918,6 +5093,11 @@
       </c>
     </row>
     <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>Españita</t>
@@ -3931,6 +5111,11 @@
       </c>
     </row>
     <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>Huamantla</t>
@@ -3944,6 +5129,11 @@
       </c>
     </row>
     <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>Hueyotlipan</t>
@@ -3957,9 +5147,14 @@
       </c>
     </row>
     <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
-          <t>Ixtacuixtla de Mariano Matamoros</t>
+          <t>Ixtacuixtla De Mariano Matamoros</t>
         </is>
       </c>
       <c r="C267">
@@ -3970,9 +5165,14 @@
       </c>
     </row>
     <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
-          <t>Muñoz de Domingo Arenas</t>
+          <t>Muñoz De Domingo Arenas</t>
         </is>
       </c>
       <c r="C268">
@@ -3983,6 +5183,11 @@
       </c>
     </row>
     <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>Panotla</t>
@@ -3996,6 +5201,11 @@
       </c>
     </row>
     <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>San José Teacalco</t>
@@ -4009,6 +5219,11 @@
       </c>
     </row>
     <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B271" t="inlineStr">
         <is>
           <t>Santa Cruz Tlaxcala</t>
@@ -4022,9 +5237,14 @@
       </c>
     </row>
     <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B272" t="inlineStr">
         <is>
-          <t>Tepetitla de Lardizábal</t>
+          <t>Tepetitla De Lardizábal</t>
         </is>
       </c>
       <c r="C272">
@@ -4035,6 +5255,11 @@
       </c>
     </row>
     <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B273" t="inlineStr">
         <is>
           <t>Tepeyanco</t>
@@ -4048,6 +5273,11 @@
       </c>
     </row>
     <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B274" t="inlineStr">
         <is>
           <t>Tlaxcala</t>
@@ -4061,6 +5291,11 @@
       </c>
     </row>
     <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B275" t="inlineStr">
         <is>
           <t>Tlaxco</t>
@@ -4074,6 +5309,11 @@
       </c>
     </row>
     <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B276" t="inlineStr">
         <is>
           <t>Tzompantepec</t>
@@ -4087,6 +5327,11 @@
       </c>
     </row>
     <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B277" t="inlineStr">
         <is>
           <t>Xaloztoc</t>
@@ -4100,6 +5345,11 @@
       </c>
     </row>
     <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B278" t="inlineStr">
         <is>
           <t>Xaltocan</t>
@@ -4113,6 +5363,11 @@
       </c>
     </row>
     <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B279" t="inlineStr">
         <is>
           <t>Yauhquemehcan</t>
@@ -4126,6 +5381,11 @@
       </c>
     </row>
     <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B280" t="inlineStr">
         <is>
           <t>Zacatelco</t>
@@ -4139,6 +5399,11 @@
       </c>
     </row>
     <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>Tlaxcala</t>
+        </is>
+      </c>
       <c r="B281" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4170,6 +5435,11 @@
       </c>
     </row>
     <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B283" t="inlineStr">
         <is>
           <t>Córdoba</t>
@@ -4183,6 +5453,11 @@
       </c>
     </row>
     <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B284" t="inlineStr">
         <is>
           <t>Coyutla</t>
@@ -4196,6 +5471,11 @@
       </c>
     </row>
     <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B285" t="inlineStr">
         <is>
           <t>Isla</t>
@@ -4209,9 +5489,14 @@
       </c>
     </row>
     <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B286" t="inlineStr">
         <is>
-          <t>Martínez de la Torre</t>
+          <t>Martínez De La Torre</t>
         </is>
       </c>
       <c r="C286">
@@ -4222,6 +5507,11 @@
       </c>
     </row>
     <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B287" t="inlineStr">
         <is>
           <t>Mecayapan</t>
@@ -4235,6 +5525,11 @@
       </c>
     </row>
     <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B288" t="inlineStr">
         <is>
           <t>Pánuco</t>
@@ -4248,6 +5543,11 @@
       </c>
     </row>
     <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B289" t="inlineStr">
         <is>
           <t>San Andrés Tuxtla</t>
@@ -4261,6 +5561,11 @@
       </c>
     </row>
     <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B290" t="inlineStr">
         <is>
           <t>Tlalixcoyan</t>
@@ -4274,6 +5579,11 @@
       </c>
     </row>
     <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B291" t="inlineStr">
         <is>
           <t>Veracruz</t>
@@ -4287,6 +5597,11 @@
       </c>
     </row>
     <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B292" t="inlineStr">
         <is>
           <t>Xalapa</t>
@@ -4300,6 +5615,11 @@
       </c>
     </row>
     <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Veracruz</t>
+        </is>
+      </c>
       <c r="B293" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4331,6 +5651,11 @@
       </c>
     </row>
     <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B295" t="inlineStr">
         <is>
           <t>Chalchihuites</t>
@@ -4344,6 +5669,11 @@
       </c>
     </row>
     <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B296" t="inlineStr">
         <is>
           <t>Fresnillo</t>
@@ -4357,6 +5687,11 @@
       </c>
     </row>
     <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B297" t="inlineStr">
         <is>
           <t>Genaro Codina</t>
@@ -4370,6 +5705,11 @@
       </c>
     </row>
     <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B298" t="inlineStr">
         <is>
           <t>Guadalupe</t>
@@ -4383,6 +5723,11 @@
       </c>
     </row>
     <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B299" t="inlineStr">
         <is>
           <t>Jalpa</t>
@@ -4396,6 +5741,11 @@
       </c>
     </row>
     <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B300" t="inlineStr">
         <is>
           <t>Juchipila</t>
@@ -4409,6 +5759,11 @@
       </c>
     </row>
     <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B301" t="inlineStr">
         <is>
           <t>Mazapil</t>
@@ -4422,6 +5777,11 @@
       </c>
     </row>
     <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B302" t="inlineStr">
         <is>
           <t>Morelos</t>
@@ -4435,9 +5795,14 @@
       </c>
     </row>
     <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B303" t="inlineStr">
         <is>
-          <t>Nochistlán de Mejía</t>
+          <t>Nochistlán De Mejía</t>
         </is>
       </c>
       <c r="C303">
@@ -4448,6 +5813,11 @@
       </c>
     </row>
     <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B304" t="inlineStr">
         <is>
           <t>Sain Alto</t>
@@ -4461,6 +5831,11 @@
       </c>
     </row>
     <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B305" t="inlineStr">
         <is>
           <t>Sombrerete</t>
@@ -4474,9 +5849,14 @@
       </c>
     </row>
     <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Tlaltenango de Sánchez Román</t>
+          <t>Tlaltenango De Sánchez Román</t>
         </is>
       </c>
       <c r="C306">
@@ -4487,6 +5867,11 @@
       </c>
     </row>
     <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B307" t="inlineStr">
         <is>
           <t>Valparaíso</t>
@@ -4500,9 +5885,14 @@
       </c>
     </row>
     <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B308" t="inlineStr">
         <is>
-          <t>Villa de Cos</t>
+          <t>Villa De Cos</t>
         </is>
       </c>
       <c r="C308">
@@ -4513,6 +5903,11 @@
       </c>
     </row>
     <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B309" t="inlineStr">
         <is>
           <t>Zacatecas</t>
@@ -4526,6 +5921,11 @@
       </c>
     </row>
     <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Zacatecas</t>
+        </is>
+      </c>
       <c r="B310" t="inlineStr">
         <is>
           <t>Total</t>
@@ -4549,41 +5949,6 @@
       </c>
       <c r="D311">
         <v>1</v>
-      </c>
-    </row>
-    <row r="313">
-      <c r="A313" t="inlineStr">
-        <is>
-          <t>Tamaño de la muestra: 794,748</t>
-        </is>
-      </c>
-    </row>
-    <row r="314">
-      <c r="A314" t="inlineStr">
-        <is>
-          <t>Fuente: Expedición de Matrículas Consulares de Alta Seguridad en los Consulados de México en E.E.U.U.</t>
-        </is>
-      </c>
-    </row>
-    <row r="315">
-      <c r="A315" t="inlineStr">
-        <is>
-          <t>Elaborado por: Análisis de Información, Instituto de los Mexicanos en el Exterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="316">
-      <c r="A316" t="inlineStr">
-        <is>
-          <t>Secretaría de Relaciones Exteriores</t>
-        </is>
-      </c>
-    </row>
-    <row r="317">
-      <c r="A317" t="inlineStr">
-        <is>
-          <t>Diciembre de 2019</t>
-        </is>
       </c>
     </row>
   </sheetData>
